--- a/NECP Scenario/Results/Regional Results/LESVOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/LESVOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.905794064294362E-08</v>
+        <v>5.762415580806548E-08</v>
       </c>
       <c r="C3">
-        <v>2.268129975186198E-08</v>
+        <v>3.345936975708855E-08</v>
       </c>
       <c r="D3">
-        <v>0.06391438279660616</v>
+        <v>0.06855344625667792</v>
       </c>
       <c r="E3">
-        <v>0.06642436082947896</v>
+        <v>0.07226714046683751</v>
       </c>
       <c r="F3">
-        <v>0.06977703854469837</v>
+        <v>0.07445171334142893</v>
       </c>
       <c r="G3">
-        <v>0.05515879834526103</v>
+        <v>0.1283685584832433</v>
       </c>
       <c r="H3">
-        <v>0.061734490779222</v>
+        <v>0.1304735193094851</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.319924954872392E-08</v>
+        <v>4.898053243865574E-08</v>
       </c>
       <c r="C4">
-        <v>1.927910479130453E-08</v>
+        <v>2.844046429532534E-08</v>
       </c>
       <c r="D4">
-        <v>0.05432722537713372</v>
+        <v>0.05827042931818247</v>
       </c>
       <c r="E4">
-        <v>0.05646070670509092</v>
+        <v>0.06142706939681618</v>
       </c>
       <c r="F4">
-        <v>0.05931048276299941</v>
+        <v>0.06328395634021106</v>
       </c>
       <c r="G4">
-        <v>0.04688497859346889</v>
+        <v>0.1091132747107588</v>
       </c>
       <c r="H4">
-        <v>0.05247431716233862</v>
+        <v>0.1109024914130611</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.2430901863046223</v>
+        <v>0.2430901876908813</v>
       </c>
       <c r="C14">
-        <v>0.2765856021476507</v>
+        <v>0.276585602760379</v>
       </c>
       <c r="D14">
-        <v>0.3052289959608691</v>
+        <v>0.3052289854310187</v>
       </c>
       <c r="E14">
-        <v>0.3666817991801249</v>
+        <v>0.3545023045181454</v>
       </c>
       <c r="F14">
-        <v>0.3612600830534551</v>
+        <v>0.3535397368730852</v>
       </c>
       <c r="G14">
-        <v>0.4087117053336412</v>
+        <v>0.4069548471778652</v>
       </c>
       <c r="H14">
-        <v>0.5411362521745245</v>
+        <v>0.541136485469468</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.5449400857072313</v>
+        <v>0.5449401085496974</v>
       </c>
       <c r="C28">
-        <v>0.6379069340474474</v>
+        <v>0.637906945147693</v>
       </c>
       <c r="D28">
-        <v>0.2294455561619103</v>
+        <v>0.2243395585471777</v>
       </c>
       <c r="E28">
-        <v>4.580807689260271E-08</v>
+        <v>6.8193055540537E-08</v>
       </c>
       <c r="F28">
-        <v>4.422446395632457E-08</v>
+        <v>6.536917675926123E-08</v>
       </c>
       <c r="G28">
-        <v>0.001104064031066223</v>
+        <v>0.000914521725659145</v>
       </c>
       <c r="H28">
-        <v>0.001937635310021581</v>
+        <v>0.001543856505181474</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.2003456197325161</v>
+        <v>0.2003456281244275</v>
       </c>
       <c r="C29">
-        <v>0.2345246080990079</v>
+        <v>0.2345246121767806</v>
       </c>
       <c r="D29">
-        <v>0.08435498387326323</v>
+        <v>0.08247777886314613</v>
       </c>
       <c r="E29">
-        <v>1.682677333018873E-08</v>
+        <v>2.504966516041892E-08</v>
       </c>
       <c r="F29">
-        <v>1.623777564007483E-08</v>
+        <v>2.400145426070135E-08</v>
       </c>
       <c r="G29">
-        <v>0.0004059058625781691</v>
+        <v>0.0003362211766075325</v>
       </c>
       <c r="H29">
-        <v>0.0007123657335896703</v>
+        <v>0.0005675940240635474</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.1363091664402465</v>
+        <v>0.1388832600083324</v>
       </c>
       <c r="E30">
-        <v>0.1833415123993616</v>
+        <v>0.1583488855263845</v>
       </c>
       <c r="F30">
-        <v>0.2294759445297918</v>
+        <v>0.1983979566975183</v>
       </c>
       <c r="G30">
-        <v>0.2724881039890805</v>
+        <v>0.276875736564764</v>
       </c>
       <c r="H30">
-        <v>0.3388568785377877</v>
+        <v>0.3276747992408861</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.01345184905362826</v>
+        <v>0.01345184758934642</v>
       </c>
       <c r="C31">
-        <v>0.01345185077878359</v>
+        <v>0.01345185013783753</v>
       </c>
       <c r="D31">
-        <v>0.01121690851225369</v>
+        <v>0.01131521418924042</v>
       </c>
       <c r="E31">
-        <v>0.01345097880950392</v>
+        <v>0.01345059525757303</v>
       </c>
       <c r="F31">
-        <v>0.01345053009464676</v>
+        <v>0.01344976895407034</v>
       </c>
       <c r="G31">
-        <v>0.01344966443480615</v>
+        <v>0.01344854186196953</v>
       </c>
       <c r="H31">
-        <v>0.01343808944575636</v>
+        <v>0.01343143246061401</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>4.616116627676162E-08</v>
+        <v>6.826370933610941E-08</v>
       </c>
       <c r="E32">
-        <v>3.838740978412286E-07</v>
+        <v>0.01217988643403977</v>
       </c>
       <c r="F32">
-        <v>0.08528150292852547</v>
+        <v>0.09317619098067825</v>
       </c>
       <c r="G32">
-        <v>0.1231188074531113</v>
+        <v>0.1249158290221572</v>
       </c>
       <c r="H32">
-        <v>0.1267076859568903</v>
+        <v>0.1267076925383069</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.01401487926121704</v>
+        <v>0.01401487789137662</v>
       </c>
       <c r="C33">
-        <v>0.01401488086556732</v>
+        <v>0.01401488026147379</v>
       </c>
       <c r="D33">
-        <v>0.01401485736626602</v>
+        <v>0.01401484580629949</v>
       </c>
       <c r="E33">
-        <v>0.01401486520930339</v>
+        <v>0.01401485732998449</v>
       </c>
       <c r="F33">
-        <v>0.01383623989982657</v>
+        <v>0.01366189805545891</v>
       </c>
       <c r="G33">
-        <v>0.01343598467552423</v>
+        <v>0.01339582130252127</v>
       </c>
       <c r="H33">
-        <v>0.01386938122965214</v>
+        <v>0.01386914159738615</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.06609097277443925</v>
+        <v>0.06602693482228954</v>
       </c>
       <c r="E36">
-        <v>0.3304382090144231</v>
+        <v>0.3129862384716909</v>
       </c>
       <c r="F36">
-        <v>0.3594570568709287</v>
+        <v>0.3685646175909814</v>
       </c>
       <c r="G36">
-        <v>0.3556039305726779</v>
+        <v>0.3616896832110665</v>
       </c>
       <c r="H36">
-        <v>0.3376606080569252</v>
+        <v>0.3456673661660675</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.03425374762194883</v>
+        <v>0.03425374491034549</v>
       </c>
       <c r="C37">
-        <v>0.03425375081569763</v>
+        <v>0.03425374962930561</v>
       </c>
       <c r="D37">
-        <v>0.02307328498981162</v>
+        <v>0.02303797749380357</v>
       </c>
       <c r="E37">
-        <v>0.0306940436261547</v>
+        <v>0.0307284574564256</v>
       </c>
       <c r="F37">
-        <v>0.03051288400376786</v>
+        <v>0.03006791204187888</v>
       </c>
       <c r="G37">
-        <v>0.03025726372351956</v>
+        <v>0.02974347184365241</v>
       </c>
       <c r="H37">
-        <v>0.02961082820457424</v>
+        <v>0.02926043258512982</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1.16141145300725E-08</v>
+        <v>1.715984009190733E-08</v>
       </c>
       <c r="C38">
-        <v>5.090860127432397E-09</v>
+        <v>7.522291746932969E-09</v>
       </c>
       <c r="D38">
-        <v>0.0526035598798056</v>
+        <v>0.05205963687339813</v>
       </c>
       <c r="E38">
-        <v>0.03311071341562114</v>
+        <v>0.02988256490397829</v>
       </c>
       <c r="F38">
-        <v>0.03725391227744779</v>
+        <v>0.04325195603738589</v>
       </c>
       <c r="G38">
-        <v>0.04335661859940999</v>
+        <v>0.05206437224407547</v>
       </c>
       <c r="H38">
-        <v>0.05995520112924259</v>
+        <v>0.06634099019616435</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.905794064294362E-08</v>
+        <v>5.762415580806548E-08</v>
       </c>
       <c r="C40">
-        <v>2.268129975186198E-08</v>
+        <v>3.345936975708855E-08</v>
       </c>
       <c r="D40">
-        <v>0.06391438279660616</v>
+        <v>0.06855344625667792</v>
       </c>
       <c r="E40">
-        <v>0.06642436082947896</v>
+        <v>0.07226714046683751</v>
       </c>
       <c r="F40">
-        <v>0.06977703854469837</v>
+        <v>0.07445171334142893</v>
       </c>
       <c r="G40">
-        <v>0.05515879834526103</v>
+        <v>0.1283685584832433</v>
       </c>
       <c r="H40">
-        <v>0.061734490779222</v>
+        <v>0.1304735193094851</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>3.319924954872392E-08</v>
+        <v>4.898053243865574E-08</v>
       </c>
       <c r="C41">
-        <v>1.927910479130453E-08</v>
+        <v>2.844046429532534E-08</v>
       </c>
       <c r="D41">
-        <v>0.05432722537713372</v>
+        <v>0.05827042931818247</v>
       </c>
       <c r="E41">
-        <v>0.05646070670509092</v>
+        <v>0.06142706939681618</v>
       </c>
       <c r="F41">
-        <v>0.05931048276299941</v>
+        <v>0.06328395634021106</v>
       </c>
       <c r="G41">
-        <v>0.04688497859346889</v>
+        <v>0.1091132747107588</v>
       </c>
       <c r="H41">
-        <v>0.05247431716233862</v>
+        <v>0.1109024914130611</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.8586910942197E-09</v>
+        <v>-8.64362336940974E-09</v>
       </c>
       <c r="C42">
-        <v>-3.40219496055745E-09</v>
+        <v>-5.01890546176321E-09</v>
       </c>
       <c r="D42">
-        <v>-0.009587157419472442</v>
+        <v>-0.01028301693849545</v>
       </c>
       <c r="E42">
-        <v>-0.009963654124388044</v>
+        <v>-0.01084007107002133</v>
       </c>
       <c r="F42">
-        <v>-0.01046655578169896</v>
+        <v>-0.01116775700121787</v>
       </c>
       <c r="G42">
-        <v>-0.008273819751792137</v>
+        <v>-0.01925528377248455</v>
       </c>
       <c r="H42">
-        <v>-0.009260173616883381</v>
+        <v>-0.019571027896424</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-0.1737960053085204</v>
+        <v>-0.142937085207179</v>
       </c>
       <c r="F43">
-        <v>-0.2537971380880277</v>
+        <v>-0.2385576886556581</v>
       </c>
       <c r="G43">
-        <v>-0.246878288201777</v>
+        <v>-0.2475783226200463</v>
       </c>
       <c r="H43">
-        <v>-0.158838746691479</v>
+        <v>-0.144850508609571</v>
       </c>
     </row>
     <row r="44" spans="1:8">
